--- a/docs/week2/05_第二周验收台账.xlsx
+++ b/docs/week2/05_第二周验收台账.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc62b2df854e2454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="2" r:id="R73996b13a3f14676"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="3" r:id="R6efd25cc61674fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="4" r:id="R6c6f3ba127354399"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="5" r:id="R876ea38a596348af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用户功能验收" sheetId="6" r:id="Rebf77bcbd6b54194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本复评" sheetId="7" r:id="Rb264d946fcb943c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="8" r:id="R928ac8526b0d4759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc40e654825d0487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="2" r:id="Rf0651d3fff4f45e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="3" r:id="R35e483e685cd46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="4" r:id="Rda23ce00507f43ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="5" r:id="R81af503100b046ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用户功能验收" sheetId="6" r:id="R0230a3117064415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本复评" sheetId="7" r:id="R54712443fac945e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="8" r:id="Raf0a52559a344bea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -775,13 +775,13 @@
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -826,9 +826,11 @@
       <x:c r="C2" s="7" t="str">
         <x:v>LAN 另一设备首页/healthz/搜索/详情</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str"/>
+      <x:c r="D2" s="7" t="str">
+        <x:v>首页/搜索/healthz 截图已收；设备/详情/录屏待补</x:v>
+      </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>evidence/week2/A/lan-device-*.png</x:v>
+        <x:v>evidence/week2/A/lan-home.png; lan-search.png; lan-healthz.png</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str"/>
       <x:c r="G2" s="7" t="str"/>
@@ -837,7 +839,7 @@
       </x:c>
       <x:c r="I2" s="7" t="str">
         <x:f>IF(AND(D2&lt;&gt;"",E2&lt;&gt;"",F2&lt;&gt;"",G2&lt;&gt;"",H2=TRUE),"通过",IF(D2="","待填写",IF(E2="","缺证据",IF(OR(F2="",G2=""),"待接收","未达标"))))</x:f>
-        <x:v>待填写</x:v>
+        <x:v>待接收</x:v>
       </x:c>
       <x:c r="J2" s="7" t="str"/>
     </x:row>
@@ -3399,7 +3401,7 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>evidence/week2/A/lan-device.png</x:v>
+        <x:v>evidence/week2/A/lan-home.png; lan-search.png; lan-healthz.png</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>截图</x:v>
@@ -3407,7 +3409,7 @@
       <x:c r="E2" s="7" t="str"/>
       <x:c r="F2" s="7" t="str"/>
       <x:c r="G2" s="7" t="str">
-        <x:v>待补</x:v>
+        <x:v>已收到，待补设备/时间</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">

--- a/docs/week2/05_第二周验收台账.xlsx
+++ b/docs/week2/05_第二周验收台账.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>首页/搜索/healthz 三张截图已收；访问设备：ASUS Vivobook S Flip（TN3604YA，Windows 11，192.168.43.110→组长机 192.168.43.50:5000）；访问时间 2026-09-19 20:36；详情页截图待补</t>
+          <t>首页/搜索/healthz 三张截图已收；访问设备：ASUS Vivobook S Flip（TN3604YA，Windows 11，192.168.43.110→LAN 服务 192.168.43.50:5000）；访问时间 2026-09-19 20:36；C 确认无需补详情页截图</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -964,8 +964,16 @@
           <t>evidence/week2/A/lan-home.png; lan-search.png; lan-healthz.png</t>
         </is>
       </c>
-      <c r="F2" s="8" t="str"/>
-      <c r="G2" s="8" t="str"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>3a34ea5（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-21 确认接收（沟通记录，见 lan-verification.md）</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="b">
         <v>0</v>
       </c>
@@ -993,15 +1001,19 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>已覆盖测试</t>
+          <t>pytest 30/30 + 真实 HTTP 活体验证 4 场景全 PASS（开关关闭 404 / 6 种伪造 header 提权失败 / 开关显式开启才可用）</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>tests/core/test_api.py</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="str"/>
+          <t>evidence/week2/A/role-isolation-live.txt; role-isolation-test-output.txt; auth-contract.md; scripts/run_role_isolation.py</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>4fe2b69（feat/week2-A-platform）</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="str"/>
       <c r="H3" s="8" t="b">
         <v>1</v>
@@ -3960,11 +3972,19 @@
           <t>截图</t>
         </is>
       </c>
-      <c r="E2" s="8" t="str"/>
-      <c r="F2" s="8" t="str"/>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>3a34ea5（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-21 确认接收</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>设备/时间已补记（2026-09-21，见 lan-verification.md），详情页截图待补</t>
+          <t>已接收（C 2026-09-21，无需补详情页）</t>
         </is>
       </c>
     </row>

--- a/docs/week2/05_第二周验收台账.xlsx
+++ b/docs/week2/05_第二周验收台账.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>4fe2b69（feat/week2-A-platform）</t>
+          <t>f88e52f06f（feat/week2-A-platform）</t>
         </is>
       </c>
       <c r="G3" s="8" t="str"/>
@@ -1040,22 +1040,31 @@
           <t>SQLite 备份恢复后三类行数一致</t>
         </is>
       </c>
-      <c r="D4" s="8" t="str"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>evidence/week2/A/backup-restore.json</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="str"/>
-      <c r="G4" s="8" t="str"/>
-      <c r="H4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8">
-        <f>IF(AND(D4&lt;&gt;"",E4&lt;&gt;"",F4&lt;&gt;"",G4&lt;&gt;"",H4=TRUE),"通过",IF(D4="","待填写",IF(E4="","缺证据",IF(OR(F4="",G4=""),"待接收","未达标"))))</f>
-        <v/>
-      </c>
-      <c r="J4" s="8" t="str"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data/app.db (5/7/11) → 模拟破坏 (3/4/5) → 恢复到 data/app-restored.db (5/7/11，SHA b343c3b4…077d076 与备份一致)；6 个敏感字段全 NULL、非敏感字段保留；篡改检测 exit=2、错误路径 exit=3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence/week2/A/backup-recovery.md; _artifacts/step1-step6.txt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bb160a1（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="G4"/>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禁字面量扫描 0 命中；A-03 验收项关闭，C 接收确认待补</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="1">
       <c r="A5" s="8" t="inlineStr">

--- a/docs/week2/05_第二周验收台账.xlsx
+++ b/docs/week2/05_第二周验收台账.xlsx
@@ -1082,26 +1082,31 @@
           <t>HTTPS/CAS 条件式结论</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>未提供服务器/域名/CAS</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>progress/week2/A/deployment-blocker.md</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="str"/>
-      <c r="G5" s="8" t="str"/>
-      <c r="H5" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8">
-        <f>IF(AND(D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"",G5&lt;&gt;"",H5=TRUE),"通过",IF(D5="","待填写",IF(E5="","缺证据",IF(OR(F5="",G5=""),"待接收","未达标"))))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8" t="str"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81.70.40.146 TCP/22 通 (RTT 11.7ms) + 80/443 拒绝 + SSH ubuntu+lm@1215 认证失败（AuthenticationException）</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence/week2/A/deployment-precheck.md; progress/week2/A/deployment-blocker.md (9/24 升级版)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3c953547b1ec (feat/week2-A-platform)</t>
+        </is>
+      </c>
+      <c r="G5"/>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A-04 阻塞；按任务书 §一不宣称上线；缺 5 项外部资源见 blocker.md §二</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="1">
       <c r="A6" s="8" t="n"/>

--- a/docs/week2/05_第二周验收台账.xlsx
+++ b/docs/week2/05_第二周验收台账.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A验收" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B验收" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="C验收" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="协作交接" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="用户功能验收" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="20样本复评" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="证据索引" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用户功能验收" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本复评" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -443,7 +443,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>待补实际值</t>
+          <t>第一周台账已回填终版（ca0aa06→db08e36：gold v2.1、裁决后口径、B-17/B-18 增补）</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -451,7 +451,11 @@
           <t>docs/week1/05_本周验收台账.xlsx</t>
         </is>
       </c>
-      <c r="F2" s="8" t="str"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>PR #9（c/ledger-backfill）</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="str"/>
       <c r="H2" s="8" t="b">
         <v>0</v>
@@ -462,7 +466,7 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>A/C 实际值、证据、Commit/接收仍需现场填写</t>
+          <t>9/27 合并 PR #9 后本行闭环</t>
         </is>
       </c>
     </row>
@@ -525,7 +529,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>已载入旧报告，待复评</t>
+          <t>B 已复评（f2fb46e）：归一化主口径 OCR 完整记录 57.89% vs 多模态 10.53%；裁决口径差 -15.79pp；均维持不启用</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -536,7 +540,7 @@
       <c r="F4" s="8" t="str"/>
       <c r="G4" s="8" t="str"/>
       <c r="H4" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8">
         <f>IF(AND(D4&lt;&gt;"",E4&lt;&gt;"",F4&lt;&gt;"",G4&lt;&gt;"",H4=TRUE),"通过",IF(D4="","待填写",IF(E4="","缺证据",IF(OR(F4="",G4=""),"待接收","未达标"))))</f>
@@ -544,7 +548,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>严格逐样本报告保留为附件</t>
+          <t>严格逐样本报告保留为审计附件（同一报告内三口径并存）</t>
         </is>
       </c>
     </row>
@@ -975,13 +979,17 @@
         </is>
       </c>
       <c r="H2" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="8">
         <f>IF(AND(D2&lt;&gt;"",E2&lt;&gt;"",F2&lt;&gt;"",G2&lt;&gt;"",H2=TRUE),"通过",IF(D2="","待填写",IF(E2="","缺证据",IF(OR(F2="",G2=""),"待接收","未达标"))))</f>
         <v/>
       </c>
-      <c r="J2" s="8" t="str"/>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-21 确认无需详情页截图，A-01 关闭</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="1">
       <c r="A3" s="8" t="inlineStr">
@@ -1014,7 +1022,11 @@
           <t>f88e52f06f（feat/week2-A-platform）</t>
         </is>
       </c>
-      <c r="G3" s="8" t="str"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收（合并 e2510db，全量回归 226 tests 通过）</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="b">
         <v>1</v>
       </c>
@@ -1042,27 +1054,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">data/app.db (5/7/11) → 模拟破坏 (3/4/5) → 恢复到 data/app-restored.db (5/7/11，SHA b343c3b4…077d076 与备份一致)；6 个敏感字段全 NULL、非敏感字段保留；篡改检测 exit=2、错误路径 exit=3</t>
+          <t>data/app.db (5/7/11) → 模拟破坏 (3/4/5) → 恢复到 data/app-restored.db (5/7/11，SHA b343c3b4…077d076 与备份一致)；6 个敏感字段全 NULL、非敏感字段保留；篡改检测 exit=2、错误路径 exit=3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">evidence/week2/A/backup-recovery.md; _artifacts/step1-step6.txt</t>
+          <t>evidence/week2/A/backup-recovery.md; _artifacts/step1-step6.txt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bb160a1（feat/week2-A-platform）</t>
-        </is>
-      </c>
-      <c r="G4"/>
-      <c r="H4">
+          <t>bb160a1（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收（backup-recovery.md + _artifacts step1-6 六步证据复核）</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">禁字面量扫描 0 命中；A-03 验收项关闭，C 接收确认待补</t>
+          <t>禁字面量扫描 0 命中；A-03 验收项关闭</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1099,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">81.70.40.146 TCP/22 通 (RTT 11.7ms) + 80/443 拒绝 + SSH ubuntu+lm@1215 认证失败（AuthenticationException）</t>
+          <t>81.70.40.146 TCP/22 通 (RTT 11.7ms) + 80/443 拒绝 + SSH ubuntu+lm@1215 认证失败（AuthenticationException）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">evidence/week2/A/deployment-precheck.md; progress/week2/A/deployment-blocker.md (9/24 升级版)</t>
+          <t>evidence/week2/A/deployment-precheck.md; progress/week2/A/deployment-blocker.md (9/24 升级版)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3c953547b1ec (feat/week2-A-platform)</t>
-        </is>
-      </c>
-      <c r="G5"/>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5"/>
+          <t>3c953547b1ec (feat/week2-A-platform)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认阻塞记录成立，按阻塞收尾</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-04 阻塞；按任务书 §一不宣称上线；缺 5 项外部资源见 blocker.md §二</t>
+          <t>验收项=条件式结论：阻塞记录已交付即达标；不宣称公网上线（缺 5 项外部资源见 blocker.md §二）</t>
         </is>
       </c>
     </row>
@@ -1504,18 +1522,26 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>待烟测</t>
+          <t>导入烟测通过：articles=5 assets=4 records=7 evidence=51；整批重复导入业务表行数不变（幂等）；packs 51 条=导入 evidence 51 行</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/B/bundle-import-smoke.json</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="str"/>
-      <c r="G2" s="8" t="str"/>
+          <t>evidence/week1/B/import-smoke.txt; evidence/week2/B/bundle_import_smoke.json</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>6b779cc（feat/week2-B-quality）</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收（合并 7b791ae）</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="8">
         <f>IF(AND(D2&lt;&gt;"",E2&lt;&gt;"",F2&lt;&gt;"",G2&lt;&gt;"",H2=TRUE),"通过",IF(D2="","待填写",IF(E2="","缺证据",IF(OR(F2="",G2=""),"待接收","未达标"))))</f>
@@ -1541,18 +1567,26 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>待复评</t>
+          <t>同 20 样本/SHA-256/gold 复评：归一化主口径 OCR 完整 57.89%(11/19) vs 多模态 10.53%(2/19)；字段级明细见 20样本复评 sheet；严格+裁决口径保留</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="str"/>
-      <c r="G3" s="8" t="str"/>
+          <t>reports/extraction/evaluation_report.json; reports/extraction/eval_raw/ocr.json</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>f2fb46e（feat/week2-B-quality）</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="8">
         <f>IF(AND(D3&lt;&gt;"",E3&lt;&gt;"",F3&lt;&gt;"",G3&lt;&gt;"",H3=TRUE),"通过",IF(D3="","待填写",IF(E3="","缺证据",IF(OR(F3="",G3=""),"待接收","未达标"))))</f>
@@ -1578,7 +1612,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>已记录旧报告</t>
+          <t>规则修正后归一化：学历 100%、城市 89.47%、专业 70%、岗位 85%；低于 90% 样本与 review_required 队列保留于报告与 eval_raw 逐样本</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1587,7 +1621,11 @@
         </is>
       </c>
       <c r="F4" s="8" t="str"/>
-      <c r="G4" s="8" t="str"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收</t>
+        </is>
+      </c>
       <c r="H4" s="8" t="b">
         <v>1</v>
       </c>
@@ -1615,7 +1653,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>归一化完整记录差值=-21.06pp</t>
+          <t>归一化完整记录差值 -47.36pp（57.89 vs 10.53）；裁决口径 -15.79pp；均未达 +5pp 门槛 → 维持不启用</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1624,7 +1662,11 @@
         </is>
       </c>
       <c r="F5" s="8" t="str"/>
-      <c r="G5" s="8" t="str"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 确认接收</t>
+        </is>
+      </c>
       <c r="H5" s="8" t="b">
         <v>1</v>
       </c>
@@ -2039,7 +2081,11 @@
         </is>
       </c>
       <c r="F2" s="8" t="str"/>
-      <c r="G2" s="8" t="str"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验（226 tests + 端到端脚本）</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="b">
         <v>1</v>
       </c>
@@ -2076,7 +2122,11 @@
         </is>
       </c>
       <c r="F3" s="8" t="str"/>
-      <c r="G3" s="8" t="str"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验（默认关闭、retention_days=90）</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="b">
         <v>1</v>
       </c>
@@ -2113,7 +2163,11 @@
         </is>
       </c>
       <c r="F4" s="8" t="str"/>
-      <c r="G4" s="8" t="str"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验（incognito-zero-write.json 3 断言全绿）</t>
+        </is>
+      </c>
       <c r="H4" s="8" t="b">
         <v>1</v>
       </c>
@@ -2141,18 +2195,26 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>第一周代码已有，Network 证据待补</t>
+          <t>游客 Network 证据已补：published-only、无 source_url/person、review_required/draft 详情 404、个人接口 401、管理接口 403（12 项断言全绿）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/C/guest-network.json</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="str"/>
-      <c r="G5" s="8" t="str"/>
+          <t>evidence/week2/C/guest-network.json; cross-user-isolation.json; incognito-zero-write.json</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
       <c r="H5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="8">
         <f>IF(AND(D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"",G5&lt;&gt;"",H5=TRUE),"通过",IF(D5="","待填写",IF(E5="","缺证据",IF(OR(F5="",G5=""),"待接收","未达标"))))</f>
@@ -2556,18 +2618,26 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>已迁移，待接收登记</t>
+          <t>B 白名单六目录与 week1 终版零差异；接收范围 604170d..f2fb46e（迁移核验/导入烟测/规则修正/复评）</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>git diff --name-status origin/main..origin/feat/week1-extraction-eval</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="str"/>
-      <c r="G2" s="8" t="str"/>
+          <t>progress/week1/B/WEEK2_WHITELIST.md</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>7b791ae（merge feat/week2-B-quality→week2-integration）</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收登记；合并后 226 tests 全绿</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="8">
         <f>IF(AND(D2&lt;&gt;"",E2&lt;&gt;"",F2&lt;&gt;"",G2&lt;&gt;"",H2=TRUE),"通过",IF(D2="","待填写",IF(E2="","缺证据",IF(OR(F2="",G2=""),"待接收","未达标"))))</f>
@@ -2593,7 +2663,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>待 A 提交</t>
+          <t>LAN 证据/认证契约/备份恢复/部署阻塞均已接收并合并</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -2601,10 +2671,18 @@
           <t>evidence/week2/A/</t>
         </is>
       </c>
-      <c r="F3" s="8" t="str"/>
-      <c r="G3" s="8" t="str"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>e2510db（merge feat/week2-A-platform→week2-integration）</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="8">
         <f>IF(AND(D3&lt;&gt;"",E3&lt;&gt;"",F3&lt;&gt;"",G3&lt;&gt;"",H3=TRUE),"通过",IF(D3="","待填写",IF(E3="","缺证据",IF(OR(F3="",G3=""),"待接收","未达标"))))</f>
@@ -2630,15 +2708,19 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>待 9/25 复测</t>
+          <t>移动端 390×844/768×1024 截图×5 已归档；游客/隐私/隔离 API 证据×4 已归档；完整演示录屏待人工补齐</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/C/demo.mp4</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="str"/>
+          <t>evidence/week2/C/</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="str"/>
       <c r="H4" s="8" t="b">
         <v>0</v>
@@ -2647,7 +2729,11 @@
         <f>IF(AND(D4&lt;&gt;"",E4&lt;&gt;"",F4&lt;&gt;"",G4&lt;&gt;"",H4=TRUE),"通过",IF(D4="","待填写",IF(E4="","缺证据",IF(OR(F4="",G4=""),"待接收","未达标"))))</f>
         <v/>
       </c>
-      <c r="J4" s="8" t="str"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>录屏待人工补齐后关闭（本机浏览器录制能力不可用）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="1">
       <c r="A5" s="8" t="n"/>
@@ -3066,7 +3152,11 @@
         </is>
       </c>
       <c r="F2" s="8" t="str"/>
-      <c r="G2" s="8" t="str"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验（cross-user-isolation.json 5 断言全绿）</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="b">
         <v>1</v>
       </c>
@@ -3103,7 +3193,11 @@
         </is>
       </c>
       <c r="F3" s="8" t="str"/>
-      <c r="G3" s="8" t="str"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="b">
         <v>1</v>
       </c>
@@ -3131,18 +3225,26 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>待端到端证据</t>
+          <t>端到端已补：history_count 2 → DELETE /api/me/history → insights 0，旧记录退出画像</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/C/history-delete.json</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="str"/>
-      <c r="G4" s="8" t="str"/>
+          <t>evidence/week2/C/history-delete.json; incognito-zero-write.json</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
       <c r="H4" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8">
         <f>IF(AND(D4&lt;&gt;"",E4&lt;&gt;"",F4&lt;&gt;"",G4&lt;&gt;"",H4=TRUE),"通过",IF(D4="","待填写",IF(E4="","缺证据",IF(OR(F4="",G4=""),"待接收","未达标"))))</f>
@@ -3177,7 +3279,11 @@
         </is>
       </c>
       <c r="F5" s="8" t="str"/>
-      <c r="G5" s="8" t="str"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
       <c r="H5" s="8" t="b">
         <v>1</v>
       </c>
@@ -3498,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -3573,10 +3679,10 @@
       <c r="E2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="str"/>
+      <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
@@ -3597,27 +3703,23 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>20</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>P02 P03 P05 P06 P10 P15</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>未达标，复核</t>
+          <t>达标</t>
         </is>
       </c>
     </row>
@@ -3633,22 +3735,22 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>20</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>P01 P03 P04 P05 P07 P08 P11 P13 P14 P16 P19 P20</t>
+          <t>低于 90% 样本详见 eval_raw/ocr.json 逐样本（版面块错配与 gold 粒度个案）</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -3669,22 +3771,22 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>19</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.7895</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>P04 P05 P06 P07 P09 P10 P11 P15</t>
+          <t>低于 90% 样本详见 eval_raw/ocr.json</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -3715,12 +3817,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>P01-P19（详见报告）</t>
+          <t>低于 90% 样本详见 eval_raw/ocr.json</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -3749,10 +3851,10 @@
       <c r="E7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="8" t="str"/>
+      <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -3781,14 +3883,10 @@
       <c r="E8" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>P02 P03 P05 P06 P10</t>
-        </is>
-      </c>
+      <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -3809,27 +3907,23 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>20</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>P03 P07 P08 P16</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>未达标，复核</t>
+          <t>达标</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3949,12 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>P01 P03 P05 P06 P07 P08 P09 P10 P12 P14 P15 P16 P18 P20</t>
+          <t>低于 90% 样本详见 eval_raw/multimodal.json</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -3891,17 +3985,89 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>P05 P13 P19</t>
+          <t>低于 90% 样本详见 eval_raw/multimodal.json</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>reports/extraction/evaluation_report.json</t>
+          <t>reports/extraction/evaluation_report.json（fields_norm）</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
           <t>未达标，复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>完整记录</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>归一化主口径；严格 0/19、裁决 10/19 同报告保留</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>reports/extraction/evaluation_report.json（complete_record_norm）</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>week2 修正后基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>完整记录</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>与 OCR 差值 -47.36pp（裁决口径 -15.79pp），未达 +5pp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>reports/extraction/evaluation_report.json（complete_record_norm）</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>不启用多模态</t>
         </is>
       </c>
     </row>
@@ -3916,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -4015,7 +4181,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/A/backup-restore.json</t>
+          <t>evidence/week2/A/backup-recovery.md; _artifacts/step1-6.txt</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -4023,11 +4189,19 @@
           <t>日志</t>
         </is>
       </c>
-      <c r="E3" s="8" t="str"/>
-      <c r="F3" s="8" t="str"/>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>bb160a1（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>已接收</t>
         </is>
       </c>
     </row>
@@ -4052,11 +4226,19 @@
           <t>阻塞记录</t>
         </is>
       </c>
-      <c r="E4" s="8" t="str"/>
-      <c r="F4" s="8" t="str"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>3c95354/1c04f7b（feat/week2-A-platform）</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>已接收（阻塞成立）</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4255,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/B/bundle-import-smoke.json</t>
+          <t>evidence/week1/B/import-smoke.txt; evidence/week2/B/bundle_import_smoke.json</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -4081,11 +4263,19 @@
           <t>导入日志</t>
         </is>
       </c>
-      <c r="E5" s="8" t="str"/>
-      <c r="F5" s="8" t="str"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>6b779cc（feat/week2-B-quality）</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收</t>
+        </is>
+      </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>已接收</t>
         </is>
       </c>
     </row>
@@ -4110,11 +4300,19 @@
           <t>评测报告</t>
         </is>
       </c>
-      <c r="E6" s="8" t="str"/>
-      <c r="F6" s="8" t="str"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>f2fb46e（feat/week2-B-quality）</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 接收</t>
+        </is>
+      </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>已存在，待复评</t>
+          <t>已复评（归一化主口径）</t>
         </is>
       </c>
     </row>
@@ -4197,11 +4395,19 @@
           <t>Network</t>
         </is>
       </c>
-      <c r="E9" s="8" t="str"/>
-      <c r="F9" s="8" t="str"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>已补（12 项断言全绿）</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4424,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>evidence/week2/C/demo.mp4</t>
+          <t>evidence/week2/C/mobile-390x844-*.png; mobile-768x1024-*.png（demo 录屏待人工）</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -4226,11 +4432,19 @@
           <t>录屏</t>
         </is>
       </c>
-      <c r="E10" s="8" t="str"/>
-      <c r="F10" s="8" t="str"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 归档</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>截图已归档；录屏待人工补齐</t>
         </is>
       </c>
     </row>
@@ -4318,6 +4532,43 @@
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>已建立</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>evidence/week2/C/history-delete.json; incognito-zero-write.json; cross-user-isolation.json</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>端到端日志</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>cbc0ee6（feat/week2-integration）</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>C 2026-09-27 自验</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>已补（断言全绿）</t>
         </is>
       </c>
     </row>
